--- a/Syllabi/CSC 1300 Spring 2026 Master Schedule.xlsx
+++ b/Syllabi/CSC 1300 Spring 2026 Master Schedule.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acrockett\Documents\CSC\Spring 2026\CSC 1300\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acrockett\Documents\GitHub\CDER\CS1\CDER_TNTECH_CS1\Syllabi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D473C195-6E34-4DF8-ADB1-8F087FFAF847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6873DC48-1850-494B-B797-1C243FCDAD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11730" tabRatio="765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1300 Schedule" sheetId="6" r:id="rId1"/>
@@ -2633,12 +2633,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2654,9 +2648,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2720,6 +2711,9 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2729,212 +2723,218 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="14" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4451,25 +4451,25 @@
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" style="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.90625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" style="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.36328125" style="17" customWidth="1"/>
     <col min="4" max="4" width="40.81640625" style="8" customWidth="1"/>
     <col min="5" max="5" width="31.90625" style="11" customWidth="1"/>
-    <col min="6" max="6" width="18.7265625" style="63" customWidth="1"/>
+    <col min="6" max="6" width="18.7265625" style="161" customWidth="1"/>
     <col min="7" max="7" width="79.453125" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="8.6328125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+    <row r="1" spans="1:6" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="109" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-    </row>
-    <row r="2" spans="1:5" ht="15.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
@@ -4486,99 +4486,105 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="112.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="125" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="23">
         <v>46038</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="72" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>250</v>
       </c>
       <c r="E3" s="18"/>
-    </row>
-    <row r="4" spans="1:5" ht="4.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="112"/>
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="115"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="74" t="s">
+      <c r="F3" s="161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="4.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="111"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="114"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="72">
+      <c r="B5" s="69">
         <v>46041</v>
       </c>
-      <c r="C5" s="119" t="s">
+      <c r="C5" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="101" t="s">
+      <c r="D5" s="121" t="s">
         <v>218</v>
       </c>
-      <c r="E5" s="102"/>
-    </row>
-    <row r="6" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E5" s="122"/>
+    </row>
+    <row r="6" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="23">
         <v>46043</v>
       </c>
-      <c r="C6" s="120"/>
+      <c r="C6" s="119"/>
       <c r="D6" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="E6" s="80" t="s">
+      <c r="E6" s="77" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F6" s="161">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="23">
         <v>46045</v>
       </c>
-      <c r="C7" s="121"/>
+      <c r="C7" s="120"/>
       <c r="D7" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="E7" s="81" t="s">
+      <c r="E7" s="78" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="116"/>
-      <c r="B8" s="117"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="118"/>
-    </row>
-    <row r="9" spans="1:5" ht="24" x14ac:dyDescent="0.35">
-      <c r="A9" s="65" t="s">
+    <row r="8" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="115"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="117"/>
+    </row>
+    <row r="9" spans="1:6" ht="24" x14ac:dyDescent="0.35">
+      <c r="A9" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="66">
+      <c r="B9" s="64">
         <f>B5+7</f>
         <v>46048</v>
       </c>
-      <c r="C9" s="122" t="s">
+      <c r="C9" s="93" t="s">
         <v>219</v>
       </c>
-      <c r="D9" s="90" t="s">
+      <c r="D9" s="87" t="s">
         <v>259</v>
       </c>
-      <c r="E9" s="81" t="s">
+      <c r="E9" s="78" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="39" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="39" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
         <v>6</v>
       </c>
@@ -4586,13 +4592,16 @@
         <f>B6+7</f>
         <v>46050</v>
       </c>
-      <c r="C10" s="99"/>
+      <c r="C10" s="94"/>
       <c r="D10" s="3" t="s">
         <v>262</v>
       </c>
       <c r="E10" s="33"/>
-    </row>
-    <row r="11" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F10" s="161">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="46" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
         <v>4</v>
       </c>
@@ -4600,20 +4609,20 @@
         <f>B7+7</f>
         <v>46052</v>
       </c>
-      <c r="C11" s="100"/>
+      <c r="C11" s="95"/>
       <c r="D11" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="E11" s="80"/>
-    </row>
-    <row r="12" spans="1:5" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="92"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="94"/>
-    </row>
-    <row r="13" spans="1:5" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E11" s="77"/>
+    </row>
+    <row r="12" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="90"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="92"/>
+    </row>
+    <row r="13" spans="1:6" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
         <v>5</v>
       </c>
@@ -4621,14 +4630,17 @@
         <f>B9+7</f>
         <v>46055</v>
       </c>
-      <c r="C13" s="95" t="s">
+      <c r="C13" s="101" t="s">
         <v>235</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F13" s="161">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
         <v>6</v>
       </c>
@@ -4636,12 +4648,12 @@
         <f>B10+7</f>
         <v>46057</v>
       </c>
-      <c r="C14" s="99"/>
+      <c r="C14" s="94"/>
       <c r="D14" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
         <v>4</v>
       </c>
@@ -4649,22 +4661,22 @@
         <f>B11+7</f>
         <v>46059</v>
       </c>
-      <c r="C15" s="100"/>
+      <c r="C15" s="95"/>
       <c r="D15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="91" t="s">
+      <c r="E15" s="88" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="92"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="94"/>
-    </row>
-    <row r="17" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="90"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="92"/>
+    </row>
+    <row r="17" spans="1:6" ht="52" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
         <v>5</v>
       </c>
@@ -4672,14 +4684,17 @@
         <f>B13+7</f>
         <v>46062</v>
       </c>
-      <c r="C17" s="95" t="s">
+      <c r="C17" s="101" t="s">
         <v>234</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F17" s="161">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
         <v>6</v>
       </c>
@@ -4687,12 +4702,12 @@
         <f>B14+7</f>
         <v>46064</v>
       </c>
-      <c r="C18" s="99"/>
+      <c r="C18" s="94"/>
       <c r="D18" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
         <v>4</v>
       </c>
@@ -4700,19 +4715,19 @@
         <f>B15+7</f>
         <v>46066</v>
       </c>
-      <c r="C19" s="100"/>
+      <c r="C19" s="95"/>
       <c r="D19" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="92"/>
-      <c r="B20" s="93"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94"/>
-    </row>
-    <row r="21" spans="1:5" ht="74" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="90"/>
+      <c r="B20" s="91"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="92"/>
+    </row>
+    <row r="21" spans="1:6" ht="74" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
         <v>5</v>
       </c>
@@ -4720,17 +4735,20 @@
         <f>B17+7</f>
         <v>46069</v>
       </c>
-      <c r="C21" s="95" t="s">
+      <c r="C21" s="101" t="s">
         <v>233</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="E21" s="82" t="s">
+      <c r="E21" s="79" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F21" s="161">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
         <v>6</v>
       </c>
@@ -4738,13 +4756,13 @@
         <f>B18+7</f>
         <v>46071</v>
       </c>
-      <c r="C22" s="99"/>
+      <c r="C22" s="94"/>
       <c r="D22" s="3" t="s">
         <v>222</v>
       </c>
       <c r="E22" s="26"/>
     </row>
-    <row r="23" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
         <v>4</v>
       </c>
@@ -4752,19 +4770,19 @@
         <f>B19+7</f>
         <v>46073</v>
       </c>
-      <c r="C23" s="100"/>
+      <c r="C23" s="95"/>
       <c r="D23" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="92"/>
-      <c r="B24" s="93"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="94"/>
-    </row>
-    <row r="25" spans="1:5" ht="50" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="90"/>
+      <c r="B24" s="91"/>
+      <c r="C24" s="91"/>
+      <c r="D24" s="91"/>
+      <c r="E24" s="92"/>
+    </row>
+    <row r="25" spans="1:6" ht="50" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
         <v>5</v>
       </c>
@@ -4772,17 +4790,20 @@
         <f>B21+7</f>
         <v>46076</v>
       </c>
-      <c r="C25" s="95" t="s">
+      <c r="C25" s="101" t="s">
         <v>123</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E25" s="81" t="s">
+      <c r="E25" s="78" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F25" s="161">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
         <v>6</v>
       </c>
@@ -4790,15 +4811,15 @@
         <f>B22+7</f>
         <v>46078</v>
       </c>
-      <c r="C26" s="99"/>
+      <c r="C26" s="94"/>
       <c r="D26" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E26" s="81" t="s">
+      <c r="E26" s="78" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="39.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
         <v>4</v>
       </c>
@@ -4806,22 +4827,22 @@
         <f>B23+7</f>
         <v>46080</v>
       </c>
-      <c r="C27" s="100"/>
+      <c r="C27" s="95"/>
       <c r="D27" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="E27" s="91" t="s">
+      <c r="E27" s="88" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="92"/>
-      <c r="B28" s="93"/>
-      <c r="C28" s="93"/>
-      <c r="D28" s="93"/>
-      <c r="E28" s="94"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="90"/>
+      <c r="B28" s="91"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="91"/>
+      <c r="E28" s="92"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="22" t="s">
         <v>5</v>
       </c>
@@ -4829,15 +4850,18 @@
         <f>B25+7</f>
         <v>46083</v>
       </c>
-      <c r="C29" s="95" t="s">
+      <c r="C29" s="101" t="s">
         <v>268</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>238</v>
       </c>
       <c r="E29" s="27"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F29" s="161">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="22" t="s">
         <v>6</v>
       </c>
@@ -4845,13 +4869,13 @@
         <f>B26+7</f>
         <v>46085</v>
       </c>
-      <c r="C30" s="99"/>
+      <c r="C30" s="94"/>
       <c r="D30" s="3" t="s">
         <v>238</v>
       </c>
       <c r="E30" s="28"/>
     </row>
-    <row r="31" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="53" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
         <v>4</v>
       </c>
@@ -4859,20 +4883,20 @@
         <f>B27+7</f>
         <v>46087</v>
       </c>
-      <c r="C31" s="100"/>
+      <c r="C31" s="95"/>
       <c r="D31" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E31" s="81" t="s">
+      <c r="E31" s="78" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="130"/>
-      <c r="B32" s="131"/>
-      <c r="C32" s="131"/>
-      <c r="D32" s="131"/>
-      <c r="E32" s="132"/>
+    <row r="32" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="104"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="106"/>
     </row>
     <row r="33" spans="1:6" ht="39" x14ac:dyDescent="0.35">
       <c r="A33" s="22" t="s">
@@ -4882,11 +4906,14 @@
         <f>B29+7</f>
         <v>46090</v>
       </c>
-      <c r="C33" s="95" t="s">
+      <c r="C33" s="101" t="s">
         <v>273</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>243</v>
+      </c>
+      <c r="F33" s="161">
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="13" customHeight="1" x14ac:dyDescent="0.35">
@@ -4897,80 +4924,80 @@
         <f>B30+7</f>
         <v>46092</v>
       </c>
-      <c r="C34" s="99"/>
+      <c r="C34" s="94"/>
       <c r="D34" s="3" t="s">
         <v>121</v>
       </c>
       <c r="E34" s="34"/>
     </row>
     <row r="35" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="65" t="s">
+      <c r="A35" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="66">
+      <c r="B35" s="64">
         <f>B31+7</f>
         <v>46094</v>
       </c>
-      <c r="C35" s="100"/>
+      <c r="C35" s="95"/>
       <c r="D35" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E35" s="73"/>
-      <c r="F35" s="64"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="162"/>
     </row>
     <row r="36" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="92"/>
-      <c r="B36" s="93"/>
-      <c r="C36" s="93"/>
-      <c r="D36" s="93"/>
-      <c r="E36" s="94"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="91"/>
+      <c r="C36" s="91"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="92"/>
     </row>
     <row r="37" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="74" t="s">
+      <c r="A37" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="72">
+      <c r="B37" s="69">
         <f>B33+7</f>
         <v>46097</v>
       </c>
-      <c r="C37" s="103" t="s">
+      <c r="C37" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="104" t="s">
+      <c r="D37" s="123" t="s">
         <v>226</v>
       </c>
-      <c r="E37" s="105"/>
+      <c r="E37" s="124"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="74" t="s">
+      <c r="A38" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="72">
+      <c r="B38" s="69">
         <f>B34+7</f>
         <v>46099</v>
       </c>
-      <c r="C38" s="103"/>
-      <c r="D38" s="106"/>
-      <c r="E38" s="107"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="125"/>
+      <c r="E38" s="126"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="74" t="s">
+      <c r="A39" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="72">
+      <c r="B39" s="69">
         <f>B35+7</f>
         <v>46101</v>
       </c>
-      <c r="C39" s="103"/>
-      <c r="D39" s="108"/>
-      <c r="E39" s="109"/>
+      <c r="C39" s="89"/>
+      <c r="D39" s="127"/>
+      <c r="E39" s="128"/>
     </row>
     <row r="40" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="98"/>
-      <c r="B40" s="93"/>
-      <c r="C40" s="93"/>
-      <c r="D40" s="93"/>
-      <c r="E40" s="94"/>
+      <c r="A40" s="107"/>
+      <c r="B40" s="91"/>
+      <c r="C40" s="91"/>
+      <c r="D40" s="91"/>
+      <c r="E40" s="92"/>
     </row>
     <row r="41" spans="1:6" ht="26" x14ac:dyDescent="0.35">
       <c r="A41" s="22" t="s">
@@ -4980,13 +5007,16 @@
         <f>B37+7</f>
         <v>46104</v>
       </c>
-      <c r="C41" s="95" t="s">
+      <c r="C41" s="101" t="s">
         <v>269</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>121</v>
       </c>
       <c r="E41" s="26"/>
+      <c r="F41" s="161">
+        <v>10</v>
+      </c>
     </row>
     <row r="42" spans="1:6" ht="50" x14ac:dyDescent="0.35">
       <c r="A42" s="22" t="s">
@@ -4996,11 +5026,11 @@
         <f>B38+7</f>
         <v>46106</v>
       </c>
-      <c r="C42" s="99"/>
+      <c r="C42" s="94"/>
       <c r="D42" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E42" s="81" t="s">
+      <c r="E42" s="78" t="s">
         <v>228</v>
       </c>
     </row>
@@ -5012,19 +5042,19 @@
         <f>B39+7</f>
         <v>46108</v>
       </c>
-      <c r="C43" s="100"/>
+      <c r="C43" s="95"/>
       <c r="D43" s="3" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="98" t="s">
+      <c r="A44" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="93"/>
-      <c r="C44" s="93"/>
-      <c r="D44" s="93"/>
-      <c r="E44" s="94"/>
+      <c r="B44" s="91"/>
+      <c r="C44" s="91"/>
+      <c r="D44" s="91"/>
+      <c r="E44" s="92"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="22" t="s">
@@ -5034,11 +5064,14 @@
         <f>B41+7</f>
         <v>46111</v>
       </c>
-      <c r="C45" s="103" t="s">
+      <c r="C45" s="89" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="62" t="s">
         <v>10</v>
+      </c>
+      <c r="F45" s="161">
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -5049,32 +5082,32 @@
         <f>B42+7</f>
         <v>46113</v>
       </c>
-      <c r="C46" s="103"/>
+      <c r="C46" s="89"/>
       <c r="D46" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="26"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="74" t="s">
+      <c r="A47" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="72">
+      <c r="B47" s="69">
         <f>B43+7</f>
         <v>46115</v>
       </c>
-      <c r="C47" s="103"/>
-      <c r="D47" s="101" t="s">
+      <c r="C47" s="89"/>
+      <c r="D47" s="121" t="s">
         <v>224</v>
       </c>
-      <c r="E47" s="102"/>
+      <c r="E47" s="122"/>
     </row>
     <row r="48" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="92"/>
-      <c r="B48" s="93"/>
-      <c r="C48" s="93"/>
-      <c r="D48" s="93"/>
-      <c r="E48" s="94"/>
+      <c r="A48" s="90"/>
+      <c r="B48" s="91"/>
+      <c r="C48" s="91"/>
+      <c r="D48" s="91"/>
+      <c r="E48" s="92"/>
     </row>
     <row r="49" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="22" t="s">
@@ -5084,23 +5117,26 @@
         <f>B45+7</f>
         <v>46118</v>
       </c>
-      <c r="C49" s="95" t="s">
+      <c r="C49" s="101" t="s">
         <v>246</v>
       </c>
-      <c r="D49" s="67" t="s">
+      <c r="D49" s="65" t="s">
         <v>122</v>
       </c>
       <c r="E49" s="26"/>
+      <c r="F49" s="161">
+        <v>12</v>
+      </c>
     </row>
     <row r="50" spans="1:6" ht="26" x14ac:dyDescent="0.35">
-      <c r="A50" s="65" t="s">
+      <c r="A50" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="66">
+      <c r="B50" s="64">
         <f>B46+7</f>
         <v>46120</v>
       </c>
-      <c r="C50" s="99"/>
+      <c r="C50" s="94"/>
       <c r="D50" s="3" t="s">
         <v>274</v>
       </c>
@@ -5113,31 +5149,34 @@
         <f>B47+7</f>
         <v>46122</v>
       </c>
-      <c r="C51" s="100"/>
-      <c r="D51" s="68" t="s">
+      <c r="C51" s="95"/>
+      <c r="D51" s="66" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="98"/>
-      <c r="B52" s="93"/>
-      <c r="C52" s="93"/>
-      <c r="D52" s="93"/>
-      <c r="E52" s="94"/>
+      <c r="A52" s="107"/>
+      <c r="B52" s="91"/>
+      <c r="C52" s="91"/>
+      <c r="D52" s="91"/>
+      <c r="E52" s="92"/>
     </row>
     <row r="53" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="65" t="s">
+      <c r="A53" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="66">
+      <c r="B53" s="64">
         <f>B49+7</f>
         <v>46125</v>
       </c>
-      <c r="C53" s="95" t="s">
+      <c r="C53" s="101" t="s">
         <v>276</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="F53" s="161">
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="39" x14ac:dyDescent="0.35">
@@ -5148,11 +5187,11 @@
         <f>B50+7</f>
         <v>46127</v>
       </c>
-      <c r="C54" s="99"/>
-      <c r="D54" s="68" t="s">
+      <c r="C54" s="94"/>
+      <c r="D54" s="66" t="s">
         <v>275</v>
       </c>
-      <c r="E54" s="83" t="s">
+      <c r="E54" s="80" t="s">
         <v>229</v>
       </c>
     </row>
@@ -5164,69 +5203,71 @@
         <f>B51+7</f>
         <v>46129</v>
       </c>
-      <c r="C55" s="100"/>
+      <c r="C55" s="95"/>
       <c r="D55" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E55" s="26"/>
     </row>
     <row r="56" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="92"/>
-      <c r="B56" s="93"/>
-      <c r="C56" s="93"/>
-      <c r="D56" s="93"/>
-      <c r="E56" s="94"/>
-    </row>
-    <row r="57" spans="1:6" s="71" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="65" t="s">
+      <c r="A56" s="90"/>
+      <c r="B56" s="91"/>
+      <c r="C56" s="91"/>
+      <c r="D56" s="91"/>
+      <c r="E56" s="92"/>
+    </row>
+    <row r="57" spans="1:6" s="68" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="B57" s="66">
+      <c r="B57" s="64">
         <f>B53+7</f>
         <v>46132</v>
       </c>
-      <c r="C57" s="95" t="s">
+      <c r="C57" s="101" t="s">
         <v>277</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E57" s="69"/>
-      <c r="F57" s="70"/>
+      <c r="E57" s="67"/>
+      <c r="F57" s="163">
+        <v>14</v>
+      </c>
     </row>
     <row r="58" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="65" t="s">
+      <c r="A58" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="B58" s="66">
+      <c r="B58" s="64">
         <f>B54+7</f>
         <v>46134</v>
       </c>
-      <c r="C58" s="96"/>
-      <c r="D58" s="67" t="s">
+      <c r="C58" s="129"/>
+      <c r="D58" s="65" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="74" x14ac:dyDescent="0.35">
-      <c r="A59" s="65" t="s">
+      <c r="A59" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B59" s="66">
+      <c r="B59" s="64">
         <f>B55+7</f>
         <v>46136</v>
       </c>
-      <c r="C59" s="97"/>
+      <c r="C59" s="130"/>
       <c r="D59" s="3" t="s">
         <v>241</v>
       </c>
       <c r="E59" s="34"/>
     </row>
     <row r="60" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="92"/>
-      <c r="B60" s="93"/>
-      <c r="C60" s="93"/>
-      <c r="D60" s="93"/>
-      <c r="E60" s="94"/>
+      <c r="A60" s="90"/>
+      <c r="B60" s="91"/>
+      <c r="C60" s="91"/>
+      <c r="D60" s="91"/>
+      <c r="E60" s="92"/>
     </row>
     <row r="61" spans="1:6" ht="36" x14ac:dyDescent="0.35">
       <c r="A61" s="22" t="s">
@@ -5236,14 +5277,17 @@
         <f>B57+7</f>
         <v>46139</v>
       </c>
-      <c r="C61" s="103" t="s">
+      <c r="C61" s="89" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E61" s="81" t="s">
+      <c r="E61" s="78" t="s">
         <v>278</v>
+      </c>
+      <c r="F61" s="161">
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
@@ -5254,7 +5298,7 @@
         <f>B58+7</f>
         <v>46141</v>
       </c>
-      <c r="C62" s="103"/>
+      <c r="C62" s="89"/>
       <c r="D62" s="3" t="s">
         <v>225</v>
       </c>
@@ -5267,22 +5311,22 @@
         <f>B59+7</f>
         <v>46143</v>
       </c>
-      <c r="C63" s="103"/>
+      <c r="C63" s="89"/>
       <c r="D63" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="E63" s="81" t="s">
+      <c r="E63" s="78" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="133"/>
-      <c r="B64" s="133"/>
-      <c r="C64" s="133"/>
-      <c r="D64" s="133"/>
-      <c r="E64" s="133"/>
-    </row>
-    <row r="65" spans="1:5" ht="21" x14ac:dyDescent="0.35">
+      <c r="A64" s="108"/>
+      <c r="B64" s="108"/>
+      <c r="C64" s="108"/>
+      <c r="D64" s="108"/>
+      <c r="E64" s="108"/>
+    </row>
+    <row r="65" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A65" s="23" t="s">
         <v>5</v>
       </c>
@@ -5290,135 +5334,138 @@
         <f>B61+7</f>
         <v>46146</v>
       </c>
-      <c r="C65" s="126" t="s">
+      <c r="C65" s="99" t="s">
         <v>232</v>
       </c>
-      <c r="D65" s="127"/>
+      <c r="D65" s="100"/>
       <c r="E65" s="30" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="76" t="s">
+      <c r="F65" s="161">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="B66" s="76">
+      <c r="B66" s="73">
         <v>46147</v>
       </c>
-      <c r="C66" s="77"/>
-      <c r="D66" s="78"/>
-      <c r="E66" s="79"/>
-    </row>
-    <row r="67" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="76" t="s">
+      <c r="C66" s="74"/>
+      <c r="D66" s="75"/>
+      <c r="E66" s="76"/>
+    </row>
+    <row r="67" spans="1:6" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="B67" s="76">
+      <c r="B67" s="73">
         <v>46148</v>
       </c>
-      <c r="C67" s="77"/>
-      <c r="D67" s="78"/>
-      <c r="E67" s="79"/>
-    </row>
-    <row r="68" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C67" s="74"/>
+      <c r="D67" s="75"/>
+      <c r="E67" s="76"/>
+    </row>
+    <row r="68" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="32" t="s">
         <v>230</v>
       </c>
       <c r="B68" s="32">
         <v>46149</v>
       </c>
-      <c r="C68" s="126" t="s">
+      <c r="C68" s="99" t="s">
         <v>231</v>
       </c>
-      <c r="D68" s="127"/>
-      <c r="E68" s="129"/>
-    </row>
-    <row r="69" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D68" s="100"/>
+      <c r="E68" s="103"/>
+    </row>
+    <row r="69" spans="1:6" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="29"/>
       <c r="B69" s="29"/>
       <c r="C69" s="29"/>
       <c r="D69" s="29"/>
       <c r="E69" s="29"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="23" t="s">
         <v>5</v>
       </c>
       <c r="B70" s="23">
         <v>46153</v>
       </c>
-      <c r="C70" s="128" t="s">
+      <c r="C70" s="102" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="128"/>
-      <c r="E70" s="128"/>
-    </row>
-    <row r="71" spans="1:5" ht="194" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="123" t="s">
+      <c r="D70" s="102"/>
+      <c r="E70" s="102"/>
+    </row>
+    <row r="71" spans="1:6" ht="194" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="96" t="s">
         <v>236</v>
       </c>
-      <c r="B71" s="124"/>
-      <c r="C71" s="124"/>
-      <c r="D71" s="124"/>
-      <c r="E71" s="125"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B71" s="97"/>
+      <c r="C71" s="97"/>
+      <c r="D71" s="97"/>
+      <c r="E71" s="98"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="24"/>
       <c r="B72" s="24"/>
       <c r="C72" s="13"/>
       <c r="D72" s="6"/>
       <c r="E72" s="14"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="24"/>
       <c r="B73" s="24"/>
       <c r="C73" s="13"/>
       <c r="D73" s="6"/>
       <c r="E73" s="14"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="24"/>
       <c r="B74" s="24"/>
       <c r="C74" s="13"/>
       <c r="D74" s="6"/>
       <c r="E74" s="14"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="24"/>
       <c r="B75" s="24"/>
       <c r="C75" s="13"/>
       <c r="D75" s="6"/>
       <c r="E75" s="14"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="24"/>
       <c r="B76" s="24"/>
       <c r="C76" s="13"/>
       <c r="D76" s="6"/>
       <c r="E76" s="14"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="24"/>
       <c r="B77" s="24"/>
       <c r="C77" s="13"/>
       <c r="D77" s="6"/>
       <c r="E77" s="14"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="24"/>
       <c r="B78" s="24"/>
       <c r="C78" s="13"/>
       <c r="D78" s="6"/>
       <c r="E78" s="14"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="24"/>
       <c r="B79" s="24"/>
       <c r="C79" s="13"/>
       <c r="D79" s="6"/>
       <c r="E79" s="14"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="24"/>
       <c r="B80" s="24"/>
       <c r="C80" s="13"/>
@@ -9109,6 +9156,29 @@
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="D37:E39"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:E5"/>
     <mergeCell ref="C61:C63"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="C9:C11"/>
@@ -9125,29 +9195,6 @@
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="D37:E39"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="C49:C51"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E65" r:id="rId1" xr:uid="{879A3A15-4B80-4067-8928-3ED846013FB6}"/>
@@ -9164,50 +9211,50 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="81" t="s">
         <v>252</v>
       </c>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="82" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="83" t="s">
         <v>254</v>
       </c>
-      <c r="B2" s="87">
+      <c r="B2" s="84">
         <v>0.3</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="85" t="s">
         <v>255</v>
       </c>
-      <c r="B3" s="89">
+      <c r="B3" s="86">
         <v>0.25</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="83" t="s">
         <v>256</v>
       </c>
-      <c r="B4" s="87">
+      <c r="B4" s="84">
         <v>0.25</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="85" t="s">
         <v>257</v>
       </c>
-      <c r="B5" s="89">
+      <c r="B5" s="86">
         <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="83" t="s">
         <v>258</v>
       </c>
-      <c r="B6" s="87">
+      <c r="B6" s="84">
         <v>0.1</v>
       </c>
     </row>
@@ -9233,13 +9280,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="160" t="s">
         <v>215</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="37" t="s">
@@ -9267,10 +9314,10 @@
       <c r="A4" s="137">
         <v>1</v>
       </c>
-      <c r="B4" s="146" t="s">
+      <c r="B4" s="140" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="142" t="s">
+      <c r="C4" s="143" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="49" t="s">
@@ -9282,8 +9329,8 @@
     </row>
     <row r="5" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A5" s="138"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="136"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="133"/>
       <c r="D5" s="47" t="s">
         <v>22</v>
       </c>
@@ -9293,8 +9340,8 @@
     </row>
     <row r="6" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A6" s="138"/>
-      <c r="B6" s="147"/>
-      <c r="C6" s="136"/>
+      <c r="B6" s="141"/>
+      <c r="C6" s="133"/>
       <c r="D6" s="47" t="s">
         <v>24</v>
       </c>
@@ -9304,8 +9351,8 @@
     </row>
     <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="138"/>
-      <c r="B7" s="147"/>
-      <c r="C7" s="136"/>
+      <c r="B7" s="141"/>
+      <c r="C7" s="133"/>
       <c r="D7" s="47" t="s">
         <v>26</v>
       </c>
@@ -9313,8 +9360,8 @@
     </row>
     <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="138"/>
-      <c r="B8" s="147"/>
-      <c r="C8" s="136"/>
+      <c r="B8" s="141"/>
+      <c r="C8" s="133"/>
       <c r="D8" s="47" t="s">
         <v>27</v>
       </c>
@@ -9322,17 +9369,17 @@
     </row>
     <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="138"/>
-      <c r="B9" s="147"/>
-      <c r="C9" s="136"/>
+      <c r="B9" s="141"/>
+      <c r="C9" s="133"/>
       <c r="D9" s="47" t="s">
         <v>124</v>
       </c>
       <c r="E9" s="35"/>
     </row>
     <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="149"/>
-      <c r="B10" s="163"/>
-      <c r="C10" s="148"/>
+      <c r="A10" s="139"/>
+      <c r="B10" s="142"/>
+      <c r="C10" s="144"/>
       <c r="D10" s="57" t="s">
         <v>28</v>
       </c>
@@ -9342,10 +9389,10 @@
       <c r="A11" s="138">
         <v>2</v>
       </c>
-      <c r="B11" s="140" t="s">
+      <c r="B11" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="136" t="s">
+      <c r="C11" s="133" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="47" t="s">
@@ -9357,8 +9404,8 @@
     </row>
     <row r="12" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A12" s="138"/>
-      <c r="B12" s="140"/>
-      <c r="C12" s="136"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="133"/>
       <c r="D12" s="47" t="s">
         <v>33</v>
       </c>
@@ -9368,8 +9415,8 @@
     </row>
     <row r="13" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="138"/>
-      <c r="B13" s="140"/>
-      <c r="C13" s="136"/>
+      <c r="B13" s="131"/>
+      <c r="C13" s="133"/>
       <c r="D13" s="47" t="s">
         <v>35</v>
       </c>
@@ -9379,8 +9426,8 @@
     </row>
     <row r="14" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A14" s="138"/>
-      <c r="B14" s="140"/>
-      <c r="C14" s="136"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="133"/>
       <c r="D14" s="47" t="s">
         <v>37</v>
       </c>
@@ -9390,8 +9437,8 @@
     </row>
     <row r="15" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="138"/>
-      <c r="B15" s="140"/>
-      <c r="C15" s="136"/>
+      <c r="B15" s="131"/>
+      <c r="C15" s="133"/>
       <c r="D15" s="47" t="s">
         <v>39</v>
       </c>
@@ -9399,8 +9446,8 @@
     </row>
     <row r="16" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="138"/>
-      <c r="B16" s="140"/>
-      <c r="C16" s="136"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="133"/>
       <c r="D16" s="47" t="s">
         <v>40</v>
       </c>
@@ -9408,8 +9455,8 @@
     </row>
     <row r="17" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="138"/>
-      <c r="B17" s="140"/>
-      <c r="C17" s="136"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="133"/>
       <c r="D17" s="47" t="s">
         <v>41</v>
       </c>
@@ -9417,8 +9464,8 @@
     </row>
     <row r="18" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="138"/>
-      <c r="B18" s="140"/>
-      <c r="C18" s="136"/>
+      <c r="B18" s="131"/>
+      <c r="C18" s="133"/>
       <c r="D18" s="47" t="s">
         <v>125</v>
       </c>
@@ -9426,8 +9473,8 @@
     </row>
     <row r="19" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="138"/>
-      <c r="B19" s="141"/>
-      <c r="C19" s="143"/>
+      <c r="B19" s="132"/>
+      <c r="C19" s="134"/>
       <c r="D19" s="48" t="s">
         <v>42</v>
       </c>
@@ -9435,10 +9482,10 @@
     </row>
     <row r="20" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A20" s="138"/>
-      <c r="B20" s="144" t="s">
+      <c r="B20" s="145" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="135" t="s">
+      <c r="C20" s="148" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="46" t="s">
@@ -9448,8 +9495,8 @@
     </row>
     <row r="21" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A21" s="138"/>
-      <c r="B21" s="145"/>
-      <c r="C21" s="136"/>
+      <c r="B21" s="146"/>
+      <c r="C21" s="133"/>
       <c r="D21" s="47" t="s">
         <v>46</v>
       </c>
@@ -9457,8 +9504,8 @@
     </row>
     <row r="22" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="138"/>
-      <c r="B22" s="145"/>
-      <c r="C22" s="136"/>
+      <c r="B22" s="146"/>
+      <c r="C22" s="133"/>
       <c r="D22" s="47" t="s">
         <v>47</v>
       </c>
@@ -9466,8 +9513,8 @@
     </row>
     <row r="23" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A23" s="138"/>
-      <c r="B23" s="145"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="146"/>
+      <c r="C23" s="133"/>
       <c r="D23" s="47" t="s">
         <v>48</v>
       </c>
@@ -9475,8 +9522,8 @@
     </row>
     <row r="24" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="138"/>
-      <c r="B24" s="145"/>
-      <c r="C24" s="136"/>
+      <c r="B24" s="146"/>
+      <c r="C24" s="133"/>
       <c r="D24" s="47" t="s">
         <v>49</v>
       </c>
@@ -9484,30 +9531,30 @@
     </row>
     <row r="25" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="138"/>
-      <c r="B25" s="145"/>
-      <c r="C25" s="136"/>
+      <c r="B25" s="146"/>
+      <c r="C25" s="133"/>
       <c r="D25" s="47" t="s">
         <v>50</v>
       </c>
       <c r="E25" s="35"/>
     </row>
     <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="149"/>
-      <c r="B26" s="150"/>
-      <c r="C26" s="148"/>
+      <c r="A26" s="139"/>
+      <c r="B26" s="147"/>
+      <c r="C26" s="144"/>
       <c r="D26" s="52" t="s">
         <v>42</v>
       </c>
       <c r="E26" s="44"/>
     </row>
     <row r="27" spans="1:5" ht="39" x14ac:dyDescent="0.35">
-      <c r="A27" s="161">
+      <c r="A27" s="135">
         <v>3</v>
       </c>
-      <c r="B27" s="140" t="s">
+      <c r="B27" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="136" t="s">
+      <c r="C27" s="133" t="s">
         <v>51</v>
       </c>
       <c r="D27" s="47" t="s">
@@ -9518,9 +9565,9 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="26" x14ac:dyDescent="0.35">
-      <c r="A28" s="161"/>
-      <c r="B28" s="140"/>
-      <c r="C28" s="136"/>
+      <c r="A28" s="135"/>
+      <c r="B28" s="131"/>
+      <c r="C28" s="133"/>
       <c r="D28" s="47" t="s">
         <v>54</v>
       </c>
@@ -9529,9 +9576,9 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="26" x14ac:dyDescent="0.35">
-      <c r="A29" s="161"/>
-      <c r="B29" s="140"/>
-      <c r="C29" s="136"/>
+      <c r="A29" s="135"/>
+      <c r="B29" s="131"/>
+      <c r="C29" s="133"/>
       <c r="D29" s="47" t="s">
         <v>56</v>
       </c>
@@ -9540,9 +9587,9 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="161"/>
-      <c r="B30" s="140"/>
-      <c r="C30" s="136"/>
+      <c r="A30" s="135"/>
+      <c r="B30" s="131"/>
+      <c r="C30" s="133"/>
       <c r="D30" s="47" t="s">
         <v>58</v>
       </c>
@@ -9551,9 +9598,9 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="26" x14ac:dyDescent="0.35">
-      <c r="A31" s="161"/>
-      <c r="B31" s="140"/>
-      <c r="C31" s="136"/>
+      <c r="A31" s="135"/>
+      <c r="B31" s="131"/>
+      <c r="C31" s="133"/>
       <c r="D31" s="47" t="s">
         <v>60</v>
       </c>
@@ -9562,9 +9609,9 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="26" x14ac:dyDescent="0.35">
-      <c r="A32" s="161"/>
-      <c r="B32" s="140"/>
-      <c r="C32" s="136"/>
+      <c r="A32" s="135"/>
+      <c r="B32" s="131"/>
+      <c r="C32" s="133"/>
       <c r="D32" s="47" t="s">
         <v>62</v>
       </c>
@@ -9573,29 +9620,29 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="161"/>
-      <c r="B33" s="140"/>
-      <c r="C33" s="136"/>
+      <c r="A33" s="135"/>
+      <c r="B33" s="131"/>
+      <c r="C33" s="133"/>
       <c r="D33" s="47" t="s">
         <v>42</v>
       </c>
       <c r="E33" s="35"/>
     </row>
     <row r="34" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="161"/>
-      <c r="B34" s="141"/>
-      <c r="C34" s="143"/>
+      <c r="A34" s="135"/>
+      <c r="B34" s="132"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="48" t="s">
         <v>64</v>
       </c>
       <c r="E34" s="35"/>
     </row>
     <row r="35" spans="1:5" ht="39" x14ac:dyDescent="0.35">
-      <c r="A35" s="161"/>
-      <c r="B35" s="151" t="s">
+      <c r="A35" s="135"/>
+      <c r="B35" s="149" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="153" t="s">
+      <c r="C35" s="151" t="s">
         <v>65</v>
       </c>
       <c r="D35" s="38" t="s">
@@ -9604,67 +9651,67 @@
       <c r="E35" s="42"/>
     </row>
     <row r="36" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="161"/>
-      <c r="B36" s="152"/>
-      <c r="C36" s="154"/>
+      <c r="A36" s="135"/>
+      <c r="B36" s="150"/>
+      <c r="C36" s="152"/>
       <c r="D36" s="39" t="s">
         <v>54</v>
       </c>
       <c r="E36" s="42"/>
     </row>
     <row r="37" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="161"/>
-      <c r="B37" s="152"/>
-      <c r="C37" s="154"/>
+      <c r="A37" s="135"/>
+      <c r="B37" s="150"/>
+      <c r="C37" s="152"/>
       <c r="D37" s="39" t="s">
         <v>67</v>
       </c>
       <c r="E37" s="42"/>
     </row>
     <row r="38" spans="1:5" ht="39" x14ac:dyDescent="0.35">
-      <c r="A38" s="161"/>
-      <c r="B38" s="152"/>
-      <c r="C38" s="154"/>
+      <c r="A38" s="135"/>
+      <c r="B38" s="150"/>
+      <c r="C38" s="152"/>
       <c r="D38" s="39" t="s">
         <v>68</v>
       </c>
       <c r="E38" s="42"/>
     </row>
     <row r="39" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="161"/>
-      <c r="B39" s="152"/>
-      <c r="C39" s="154"/>
+      <c r="A39" s="135"/>
+      <c r="B39" s="150"/>
+      <c r="C39" s="152"/>
       <c r="D39" s="39" t="s">
         <v>60</v>
       </c>
       <c r="E39" s="42"/>
     </row>
     <row r="40" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="161"/>
-      <c r="B40" s="152"/>
-      <c r="C40" s="154"/>
+      <c r="A40" s="135"/>
+      <c r="B40" s="150"/>
+      <c r="C40" s="152"/>
       <c r="D40" s="39" t="s">
         <v>42</v>
       </c>
       <c r="E40" s="42"/>
     </row>
     <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="162"/>
-      <c r="B41" s="155"/>
-      <c r="C41" s="156"/>
+      <c r="A41" s="136"/>
+      <c r="B41" s="153"/>
+      <c r="C41" s="154"/>
       <c r="D41" s="43" t="s">
         <v>64</v>
       </c>
       <c r="E41" s="51"/>
     </row>
     <row r="42" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="157">
+      <c r="A42" s="155">
         <v>4</v>
       </c>
-      <c r="B42" s="158" t="s">
+      <c r="B42" s="156" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="154" t="s">
+      <c r="C42" s="152" t="s">
         <v>69</v>
       </c>
       <c r="D42" s="39" t="s">
@@ -9675,9 +9722,9 @@
       </c>
     </row>
     <row r="43" spans="1:5" ht="39" x14ac:dyDescent="0.35">
-      <c r="A43" s="157"/>
-      <c r="B43" s="158"/>
-      <c r="C43" s="154"/>
+      <c r="A43" s="155"/>
+      <c r="B43" s="156"/>
+      <c r="C43" s="152"/>
       <c r="D43" s="39" t="s">
         <v>71</v>
       </c>
@@ -9686,65 +9733,65 @@
       </c>
     </row>
     <row r="44" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="157"/>
-      <c r="B44" s="158"/>
-      <c r="C44" s="154"/>
+      <c r="A44" s="155"/>
+      <c r="B44" s="156"/>
+      <c r="C44" s="152"/>
       <c r="D44" s="39" t="s">
         <v>73</v>
       </c>
       <c r="E44" s="42"/>
     </row>
     <row r="45" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="157"/>
-      <c r="B45" s="158"/>
-      <c r="C45" s="154"/>
+      <c r="A45" s="155"/>
+      <c r="B45" s="156"/>
+      <c r="C45" s="152"/>
       <c r="D45" s="39" t="s">
         <v>126</v>
       </c>
       <c r="E45" s="42"/>
     </row>
     <row r="46" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="157"/>
-      <c r="B46" s="158"/>
-      <c r="C46" s="154"/>
+      <c r="A46" s="155"/>
+      <c r="B46" s="156"/>
+      <c r="C46" s="152"/>
       <c r="D46" s="39" t="s">
         <v>74</v>
       </c>
       <c r="E46" s="42"/>
     </row>
     <row r="47" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="157"/>
-      <c r="B47" s="158"/>
-      <c r="C47" s="154"/>
+      <c r="A47" s="155"/>
+      <c r="B47" s="156"/>
+      <c r="C47" s="152"/>
       <c r="D47" s="39" t="s">
         <v>75</v>
       </c>
       <c r="E47" s="35"/>
     </row>
     <row r="48" spans="1:5" ht="26" x14ac:dyDescent="0.35">
-      <c r="A48" s="157"/>
-      <c r="B48" s="158"/>
-      <c r="C48" s="154"/>
+      <c r="A48" s="155"/>
+      <c r="B48" s="156"/>
+      <c r="C48" s="152"/>
       <c r="D48" s="39" t="s">
         <v>76</v>
       </c>
       <c r="E48" s="35"/>
     </row>
     <row r="49" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="157"/>
-      <c r="B49" s="159"/>
-      <c r="C49" s="160"/>
+      <c r="A49" s="155"/>
+      <c r="B49" s="157"/>
+      <c r="C49" s="158"/>
       <c r="D49" s="40" t="s">
         <v>77</v>
       </c>
       <c r="E49" s="35"/>
     </row>
     <row r="50" spans="1:5" ht="26" x14ac:dyDescent="0.35">
-      <c r="A50" s="157"/>
-      <c r="B50" s="151" t="s">
+      <c r="A50" s="155"/>
+      <c r="B50" s="149" t="s">
         <v>43</v>
       </c>
-      <c r="C50" s="153" t="s">
+      <c r="C50" s="151" t="s">
         <v>69</v>
       </c>
       <c r="D50" s="38" t="s">
@@ -9753,36 +9800,36 @@
       <c r="E50" s="35"/>
     </row>
     <row r="51" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="157"/>
-      <c r="B51" s="152"/>
-      <c r="C51" s="154"/>
+      <c r="A51" s="155"/>
+      <c r="B51" s="150"/>
+      <c r="C51" s="152"/>
       <c r="D51" s="39" t="s">
         <v>128</v>
       </c>
       <c r="E51" s="35"/>
     </row>
     <row r="52" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="157"/>
-      <c r="B52" s="152"/>
-      <c r="C52" s="154"/>
+      <c r="A52" s="155"/>
+      <c r="B52" s="150"/>
+      <c r="C52" s="152"/>
       <c r="D52" s="39" t="s">
         <v>75</v>
       </c>
       <c r="E52" s="35"/>
     </row>
     <row r="53" spans="1:5" ht="26" x14ac:dyDescent="0.35">
-      <c r="A53" s="157"/>
-      <c r="B53" s="152"/>
-      <c r="C53" s="154"/>
+      <c r="A53" s="155"/>
+      <c r="B53" s="150"/>
+      <c r="C53" s="152"/>
       <c r="D53" s="39" t="s">
         <v>79</v>
       </c>
       <c r="E53" s="35"/>
     </row>
     <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="157"/>
-      <c r="B54" s="152"/>
-      <c r="C54" s="154"/>
+      <c r="A54" s="155"/>
+      <c r="B54" s="150"/>
+      <c r="C54" s="152"/>
       <c r="D54" s="39" t="s">
         <v>77</v>
       </c>
@@ -9792,10 +9839,10 @@
       <c r="A55" s="137">
         <v>5</v>
       </c>
-      <c r="B55" s="139" t="s">
+      <c r="B55" s="159" t="s">
         <v>29</v>
       </c>
-      <c r="C55" s="142" t="s">
+      <c r="C55" s="143" t="s">
         <v>80</v>
       </c>
       <c r="D55" s="49" t="s">
@@ -9807,8 +9854,8 @@
     </row>
     <row r="56" spans="1:5" ht="39" x14ac:dyDescent="0.35">
       <c r="A56" s="138"/>
-      <c r="B56" s="140"/>
-      <c r="C56" s="136"/>
+      <c r="B56" s="131"/>
+      <c r="C56" s="133"/>
       <c r="D56" s="47" t="s">
         <v>83</v>
       </c>
@@ -9818,8 +9865,8 @@
     </row>
     <row r="57" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A57" s="138"/>
-      <c r="B57" s="140"/>
-      <c r="C57" s="136"/>
+      <c r="B57" s="131"/>
+      <c r="C57" s="133"/>
       <c r="D57" s="47" t="s">
         <v>85</v>
       </c>
@@ -9829,8 +9876,8 @@
     </row>
     <row r="58" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A58" s="138"/>
-      <c r="B58" s="140"/>
-      <c r="C58" s="136"/>
+      <c r="B58" s="131"/>
+      <c r="C58" s="133"/>
       <c r="D58" s="47" t="s">
         <v>87</v>
       </c>
@@ -9840,8 +9887,8 @@
     </row>
     <row r="59" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A59" s="138"/>
-      <c r="B59" s="140"/>
-      <c r="C59" s="136"/>
+      <c r="B59" s="131"/>
+      <c r="C59" s="133"/>
       <c r="D59" s="47" t="s">
         <v>130</v>
       </c>
@@ -9851,8 +9898,8 @@
     </row>
     <row r="60" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="138"/>
-      <c r="B60" s="140"/>
-      <c r="C60" s="136"/>
+      <c r="B60" s="131"/>
+      <c r="C60" s="133"/>
       <c r="D60" s="47" t="s">
         <v>131</v>
       </c>
@@ -9860,8 +9907,8 @@
     </row>
     <row r="61" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="138"/>
-      <c r="B61" s="140"/>
-      <c r="C61" s="136"/>
+      <c r="B61" s="131"/>
+      <c r="C61" s="133"/>
       <c r="D61" s="47" t="s">
         <v>132</v>
       </c>
@@ -9869,8 +9916,8 @@
     </row>
     <row r="62" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="138"/>
-      <c r="B62" s="140"/>
-      <c r="C62" s="136"/>
+      <c r="B62" s="131"/>
+      <c r="C62" s="133"/>
       <c r="D62" s="47" t="s">
         <v>133</v>
       </c>
@@ -9878,8 +9925,8 @@
     </row>
     <row r="63" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="138"/>
-      <c r="B63" s="140"/>
-      <c r="C63" s="136"/>
+      <c r="B63" s="131"/>
+      <c r="C63" s="133"/>
       <c r="D63" s="47" t="s">
         <v>134</v>
       </c>
@@ -9887,8 +9934,8 @@
     </row>
     <row r="64" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="138"/>
-      <c r="B64" s="140"/>
-      <c r="C64" s="136"/>
+      <c r="B64" s="131"/>
+      <c r="C64" s="133"/>
       <c r="D64" s="47" t="s">
         <v>135</v>
       </c>
@@ -9896,8 +9943,8 @@
     </row>
     <row r="65" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="138"/>
-      <c r="B65" s="141"/>
-      <c r="C65" s="143"/>
+      <c r="B65" s="132"/>
+      <c r="C65" s="134"/>
       <c r="D65" s="48" t="s">
         <v>136</v>
       </c>
@@ -9905,10 +9952,10 @@
     </row>
     <row r="66" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A66" s="138"/>
-      <c r="B66" s="144" t="s">
+      <c r="B66" s="145" t="s">
         <v>43</v>
       </c>
-      <c r="C66" s="135" t="s">
+      <c r="C66" s="148" t="s">
         <v>80</v>
       </c>
       <c r="D66" s="46" t="s">
@@ -9918,8 +9965,8 @@
     </row>
     <row r="67" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A67" s="138"/>
-      <c r="B67" s="145"/>
-      <c r="C67" s="136"/>
+      <c r="B67" s="146"/>
+      <c r="C67" s="133"/>
       <c r="D67" s="47" t="s">
         <v>138</v>
       </c>
@@ -9927,8 +9974,8 @@
     </row>
     <row r="68" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A68" s="138"/>
-      <c r="B68" s="145"/>
-      <c r="C68" s="136"/>
+      <c r="B68" s="146"/>
+      <c r="C68" s="133"/>
       <c r="D68" s="47" t="s">
         <v>139</v>
       </c>
@@ -9936,8 +9983,8 @@
     </row>
     <row r="69" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="138"/>
-      <c r="B69" s="145"/>
-      <c r="C69" s="136"/>
+      <c r="B69" s="146"/>
+      <c r="C69" s="133"/>
       <c r="D69" s="47" t="s">
         <v>132</v>
       </c>
@@ -9945,8 +9992,8 @@
     </row>
     <row r="70" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="138"/>
-      <c r="B70" s="145"/>
-      <c r="C70" s="136"/>
+      <c r="B70" s="146"/>
+      <c r="C70" s="133"/>
       <c r="D70" s="47" t="s">
         <v>133</v>
       </c>
@@ -9954,8 +10001,8 @@
     </row>
     <row r="71" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A71" s="138"/>
-      <c r="B71" s="145"/>
-      <c r="C71" s="136"/>
+      <c r="B71" s="146"/>
+      <c r="C71" s="133"/>
       <c r="D71" s="47" t="s">
         <v>134</v>
       </c>
@@ -9963,8 +10010,8 @@
     </row>
     <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="138"/>
-      <c r="B72" s="145"/>
-      <c r="C72" s="136"/>
+      <c r="B72" s="146"/>
+      <c r="C72" s="133"/>
       <c r="D72" s="47" t="s">
         <v>136</v>
       </c>
@@ -9974,10 +10021,10 @@
       <c r="A73" s="137">
         <v>6</v>
       </c>
-      <c r="B73" s="139" t="s">
+      <c r="B73" s="159" t="s">
         <v>29</v>
       </c>
-      <c r="C73" s="142" t="s">
+      <c r="C73" s="143" t="s">
         <v>90</v>
       </c>
       <c r="D73" s="49" t="s">
@@ -9989,8 +10036,8 @@
     </row>
     <row r="74" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A74" s="138"/>
-      <c r="B74" s="140"/>
-      <c r="C74" s="136"/>
+      <c r="B74" s="131"/>
+      <c r="C74" s="133"/>
       <c r="D74" s="47" t="s">
         <v>141</v>
       </c>
@@ -10000,8 +10047,8 @@
     </row>
     <row r="75" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="138"/>
-      <c r="B75" s="140"/>
-      <c r="C75" s="136"/>
+      <c r="B75" s="131"/>
+      <c r="C75" s="133"/>
       <c r="D75" s="47" t="s">
         <v>142</v>
       </c>
@@ -10009,8 +10056,8 @@
     </row>
     <row r="76" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="138"/>
-      <c r="B76" s="140"/>
-      <c r="C76" s="136"/>
+      <c r="B76" s="131"/>
+      <c r="C76" s="133"/>
       <c r="D76" s="47" t="s">
         <v>143</v>
       </c>
@@ -10018,8 +10065,8 @@
     </row>
     <row r="77" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="138"/>
-      <c r="B77" s="140"/>
-      <c r="C77" s="136"/>
+      <c r="B77" s="131"/>
+      <c r="C77" s="133"/>
       <c r="D77" s="47" t="s">
         <v>144</v>
       </c>
@@ -10027,8 +10074,8 @@
     </row>
     <row r="78" spans="1:5" ht="39" x14ac:dyDescent="0.35">
       <c r="A78" s="138"/>
-      <c r="B78" s="141"/>
-      <c r="C78" s="143"/>
+      <c r="B78" s="132"/>
+      <c r="C78" s="134"/>
       <c r="D78" s="48" t="s">
         <v>145</v>
       </c>
@@ -10036,10 +10083,10 @@
     </row>
     <row r="79" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="138"/>
-      <c r="B79" s="144" t="s">
+      <c r="B79" s="145" t="s">
         <v>43</v>
       </c>
-      <c r="C79" s="135" t="s">
+      <c r="C79" s="148" t="s">
         <v>90</v>
       </c>
       <c r="D79" s="46" t="s">
@@ -10049,8 +10096,8 @@
     </row>
     <row r="80" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="138"/>
-      <c r="B80" s="145"/>
-      <c r="C80" s="136"/>
+      <c r="B80" s="146"/>
+      <c r="C80" s="133"/>
       <c r="D80" s="47" t="s">
         <v>147</v>
       </c>
@@ -10058,8 +10105,8 @@
     </row>
     <row r="81" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="138"/>
-      <c r="B81" s="145"/>
-      <c r="C81" s="136"/>
+      <c r="B81" s="146"/>
+      <c r="C81" s="133"/>
       <c r="D81" s="47" t="s">
         <v>143</v>
       </c>
@@ -10067,8 +10114,8 @@
     </row>
     <row r="82" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="138"/>
-      <c r="B82" s="145"/>
-      <c r="C82" s="136"/>
+      <c r="B82" s="146"/>
+      <c r="C82" s="133"/>
       <c r="D82" s="47" t="s">
         <v>144</v>
       </c>
@@ -10076,8 +10123,8 @@
     </row>
     <row r="83" spans="1:5" ht="39" x14ac:dyDescent="0.35">
       <c r="A83" s="138"/>
-      <c r="B83" s="145"/>
-      <c r="C83" s="136"/>
+      <c r="B83" s="146"/>
+      <c r="C83" s="133"/>
       <c r="D83" s="47" t="s">
         <v>145</v>
       </c>
@@ -10085,8 +10132,8 @@
     </row>
     <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="138"/>
-      <c r="B84" s="145"/>
-      <c r="C84" s="136"/>
+      <c r="B84" s="146"/>
+      <c r="C84" s="133"/>
       <c r="D84" s="47" t="s">
         <v>148</v>
       </c>
@@ -10096,10 +10143,10 @@
       <c r="A85" s="137">
         <v>7</v>
       </c>
-      <c r="B85" s="139" t="s">
+      <c r="B85" s="159" t="s">
         <v>29</v>
       </c>
-      <c r="C85" s="142" t="s">
+      <c r="C85" s="143" t="s">
         <v>129</v>
       </c>
       <c r="D85" s="49" t="s">
@@ -10111,8 +10158,8 @@
     </row>
     <row r="86" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A86" s="138"/>
-      <c r="B86" s="140"/>
-      <c r="C86" s="136"/>
+      <c r="B86" s="131"/>
+      <c r="C86" s="133"/>
       <c r="D86" s="47" t="s">
         <v>150</v>
       </c>
@@ -10122,8 +10169,8 @@
     </row>
     <row r="87" spans="1:5" ht="39" x14ac:dyDescent="0.35">
       <c r="A87" s="138"/>
-      <c r="B87" s="140"/>
-      <c r="C87" s="136"/>
+      <c r="B87" s="131"/>
+      <c r="C87" s="133"/>
       <c r="D87" s="47" t="s">
         <v>151</v>
       </c>
@@ -10133,8 +10180,8 @@
     </row>
     <row r="88" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A88" s="138"/>
-      <c r="B88" s="140"/>
-      <c r="C88" s="136"/>
+      <c r="B88" s="131"/>
+      <c r="C88" s="133"/>
       <c r="D88" s="47" t="s">
         <v>152</v>
       </c>
@@ -10144,8 +10191,8 @@
     </row>
     <row r="89" spans="1:5" ht="39" x14ac:dyDescent="0.35">
       <c r="A89" s="138"/>
-      <c r="B89" s="140"/>
-      <c r="C89" s="136"/>
+      <c r="B89" s="131"/>
+      <c r="C89" s="133"/>
       <c r="D89" s="47" t="s">
         <v>153</v>
       </c>
@@ -10155,8 +10202,8 @@
     </row>
     <row r="90" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A90" s="138"/>
-      <c r="B90" s="140"/>
-      <c r="C90" s="136"/>
+      <c r="B90" s="131"/>
+      <c r="C90" s="133"/>
       <c r="D90" s="47" t="s">
         <v>154</v>
       </c>
@@ -10164,8 +10211,8 @@
     </row>
     <row r="91" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A91" s="138"/>
-      <c r="B91" s="140"/>
-      <c r="C91" s="136"/>
+      <c r="B91" s="131"/>
+      <c r="C91" s="133"/>
       <c r="D91" s="47" t="s">
         <v>155</v>
       </c>
@@ -10173,8 +10220,8 @@
     </row>
     <row r="92" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A92" s="138"/>
-      <c r="B92" s="140"/>
-      <c r="C92" s="136"/>
+      <c r="B92" s="131"/>
+      <c r="C92" s="133"/>
       <c r="D92" s="47" t="s">
         <v>156</v>
       </c>
@@ -10182,8 +10229,8 @@
     </row>
     <row r="93" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A93" s="138"/>
-      <c r="B93" s="140"/>
-      <c r="C93" s="136"/>
+      <c r="B93" s="131"/>
+      <c r="C93" s="133"/>
       <c r="D93" s="47" t="s">
         <v>157</v>
       </c>
@@ -10191,8 +10238,8 @@
     </row>
     <row r="94" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A94" s="138"/>
-      <c r="B94" s="140"/>
-      <c r="C94" s="136"/>
+      <c r="B94" s="131"/>
+      <c r="C94" s="133"/>
       <c r="D94" s="47" t="s">
         <v>158</v>
       </c>
@@ -10200,8 +10247,8 @@
     </row>
     <row r="95" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A95" s="138"/>
-      <c r="B95" s="141"/>
-      <c r="C95" s="143"/>
+      <c r="B95" s="132"/>
+      <c r="C95" s="134"/>
       <c r="D95" s="55" t="s">
         <v>204</v>
       </c>
@@ -10209,10 +10256,10 @@
     </row>
     <row r="96" spans="1:5" ht="39" x14ac:dyDescent="0.35">
       <c r="A96" s="138"/>
-      <c r="B96" s="144" t="s">
+      <c r="B96" s="145" t="s">
         <v>43</v>
       </c>
-      <c r="C96" s="135" t="s">
+      <c r="C96" s="148" t="s">
         <v>129</v>
       </c>
       <c r="D96" s="46" t="s">
@@ -10222,8 +10269,8 @@
     </row>
     <row r="97" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A97" s="138"/>
-      <c r="B97" s="145"/>
-      <c r="C97" s="136"/>
+      <c r="B97" s="146"/>
+      <c r="C97" s="133"/>
       <c r="D97" s="47" t="s">
         <v>160</v>
       </c>
@@ -10231,8 +10278,8 @@
     </row>
     <row r="98" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A98" s="138"/>
-      <c r="B98" s="145"/>
-      <c r="C98" s="136"/>
+      <c r="B98" s="146"/>
+      <c r="C98" s="133"/>
       <c r="D98" s="47" t="s">
         <v>156</v>
       </c>
@@ -10240,8 +10287,8 @@
     </row>
     <row r="99" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A99" s="138"/>
-      <c r="B99" s="145"/>
-      <c r="C99" s="136"/>
+      <c r="B99" s="146"/>
+      <c r="C99" s="133"/>
       <c r="D99" s="47" t="s">
         <v>157</v>
       </c>
@@ -10249,8 +10296,8 @@
     </row>
     <row r="100" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A100" s="138"/>
-      <c r="B100" s="145"/>
-      <c r="C100" s="136"/>
+      <c r="B100" s="146"/>
+      <c r="C100" s="133"/>
       <c r="D100" s="47" t="s">
         <v>158</v>
       </c>
@@ -10258,8 +10305,8 @@
     </row>
     <row r="101" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A101" s="138"/>
-      <c r="B101" s="145"/>
-      <c r="C101" s="136"/>
+      <c r="B101" s="146"/>
+      <c r="C101" s="133"/>
       <c r="D101" s="47" t="s">
         <v>161</v>
       </c>
@@ -10267,8 +10314,8 @@
     </row>
     <row r="102" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A102" s="138"/>
-      <c r="B102" s="145"/>
-      <c r="C102" s="136"/>
+      <c r="B102" s="146"/>
+      <c r="C102" s="133"/>
       <c r="D102" s="47" t="s">
         <v>162</v>
       </c>
@@ -10276,8 +10323,8 @@
     </row>
     <row r="103" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A103" s="138"/>
-      <c r="B103" s="145"/>
-      <c r="C103" s="136"/>
+      <c r="B103" s="146"/>
+      <c r="C103" s="133"/>
       <c r="D103" s="58" t="s">
         <v>204</v>
       </c>
@@ -10285,8 +10332,8 @@
     </row>
     <row r="104" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="138"/>
-      <c r="B104" s="145"/>
-      <c r="C104" s="136"/>
+      <c r="B104" s="146"/>
+      <c r="C104" s="133"/>
       <c r="D104" s="47" t="s">
         <v>163</v>
       </c>
@@ -10296,10 +10343,10 @@
       <c r="A105" s="137">
         <v>8</v>
       </c>
-      <c r="B105" s="139" t="s">
+      <c r="B105" s="159" t="s">
         <v>29</v>
       </c>
-      <c r="C105" s="142" t="s">
+      <c r="C105" s="143" t="s">
         <v>103</v>
       </c>
       <c r="D105" s="61" t="s">
@@ -10311,8 +10358,8 @@
     </row>
     <row r="106" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A106" s="138"/>
-      <c r="B106" s="140"/>
-      <c r="C106" s="136"/>
+      <c r="B106" s="131"/>
+      <c r="C106" s="133"/>
       <c r="D106" s="59" t="s">
         <v>165</v>
       </c>
@@ -10322,8 +10369,8 @@
     </row>
     <row r="107" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A107" s="138"/>
-      <c r="B107" s="140"/>
-      <c r="C107" s="136"/>
+      <c r="B107" s="131"/>
+      <c r="C107" s="133"/>
       <c r="D107" s="59" t="s">
         <v>166</v>
       </c>
@@ -10333,8 +10380,8 @@
     </row>
     <row r="108" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A108" s="138"/>
-      <c r="B108" s="140"/>
-      <c r="C108" s="136"/>
+      <c r="B108" s="131"/>
+      <c r="C108" s="133"/>
       <c r="D108" s="59" t="s">
         <v>167</v>
       </c>
@@ -10344,8 +10391,8 @@
     </row>
     <row r="109" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A109" s="138"/>
-      <c r="B109" s="140"/>
-      <c r="C109" s="136"/>
+      <c r="B109" s="131"/>
+      <c r="C109" s="133"/>
       <c r="D109" s="59" t="s">
         <v>168</v>
       </c>
@@ -10355,8 +10402,8 @@
     </row>
     <row r="110" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A110" s="138"/>
-      <c r="B110" s="140"/>
-      <c r="C110" s="136"/>
+      <c r="B110" s="131"/>
+      <c r="C110" s="133"/>
       <c r="D110" s="59" t="s">
         <v>169</v>
       </c>
@@ -10364,8 +10411,8 @@
     </row>
     <row r="111" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A111" s="138"/>
-      <c r="B111" s="140"/>
-      <c r="C111" s="136"/>
+      <c r="B111" s="131"/>
+      <c r="C111" s="133"/>
       <c r="D111" s="59" t="s">
         <v>170</v>
       </c>
@@ -10373,8 +10420,8 @@
     </row>
     <row r="112" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A112" s="138"/>
-      <c r="B112" s="140"/>
-      <c r="C112" s="136"/>
+      <c r="B112" s="131"/>
+      <c r="C112" s="133"/>
       <c r="D112" s="59" t="s">
         <v>205</v>
       </c>
@@ -10382,8 +10429,8 @@
     </row>
     <row r="113" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A113" s="138"/>
-      <c r="B113" s="140"/>
-      <c r="C113" s="136"/>
+      <c r="B113" s="131"/>
+      <c r="C113" s="133"/>
       <c r="D113" s="59" t="s">
         <v>171</v>
       </c>
@@ -10391,8 +10438,8 @@
     </row>
     <row r="114" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A114" s="138"/>
-      <c r="B114" s="140"/>
-      <c r="C114" s="136"/>
+      <c r="B114" s="131"/>
+      <c r="C114" s="133"/>
       <c r="D114" s="59" t="s">
         <v>172</v>
       </c>
@@ -10400,8 +10447,8 @@
     </row>
     <row r="115" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A115" s="138"/>
-      <c r="B115" s="140"/>
-      <c r="C115" s="136"/>
+      <c r="B115" s="131"/>
+      <c r="C115" s="133"/>
       <c r="D115" s="59" t="s">
         <v>206</v>
       </c>
@@ -10409,8 +10456,8 @@
     </row>
     <row r="116" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A116" s="138"/>
-      <c r="B116" s="141"/>
-      <c r="C116" s="143"/>
+      <c r="B116" s="132"/>
+      <c r="C116" s="134"/>
       <c r="D116" s="60" t="s">
         <v>207</v>
       </c>
@@ -10418,10 +10465,10 @@
     </row>
     <row r="117" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A117" s="138"/>
-      <c r="B117" s="144" t="s">
+      <c r="B117" s="145" t="s">
         <v>43</v>
       </c>
-      <c r="C117" s="135" t="s">
+      <c r="C117" s="148" t="s">
         <v>208</v>
       </c>
       <c r="D117" s="46" t="s">
@@ -10431,8 +10478,8 @@
     </row>
     <row r="118" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A118" s="138"/>
-      <c r="B118" s="145"/>
-      <c r="C118" s="136"/>
+      <c r="B118" s="146"/>
+      <c r="C118" s="133"/>
       <c r="D118" s="47" t="s">
         <v>173</v>
       </c>
@@ -10440,8 +10487,8 @@
     </row>
     <row r="119" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A119" s="138"/>
-      <c r="B119" s="145"/>
-      <c r="C119" s="136"/>
+      <c r="B119" s="146"/>
+      <c r="C119" s="133"/>
       <c r="D119" s="47" t="s">
         <v>168</v>
       </c>
@@ -10449,8 +10496,8 @@
     </row>
     <row r="120" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A120" s="138"/>
-      <c r="B120" s="145"/>
-      <c r="C120" s="136"/>
+      <c r="B120" s="146"/>
+      <c r="C120" s="133"/>
       <c r="D120" s="47" t="s">
         <v>174</v>
       </c>
@@ -10458,8 +10505,8 @@
     </row>
     <row r="121" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A121" s="138"/>
-      <c r="B121" s="145"/>
-      <c r="C121" s="136"/>
+      <c r="B121" s="146"/>
+      <c r="C121" s="133"/>
       <c r="D121" s="47" t="s">
         <v>175</v>
       </c>
@@ -10467,8 +10514,8 @@
     </row>
     <row r="122" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A122" s="138"/>
-      <c r="B122" s="145"/>
-      <c r="C122" s="136"/>
+      <c r="B122" s="146"/>
+      <c r="C122" s="133"/>
       <c r="D122" s="47" t="s">
         <v>176</v>
       </c>
@@ -10476,8 +10523,8 @@
     </row>
     <row r="123" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A123" s="138"/>
-      <c r="B123" s="145"/>
-      <c r="C123" s="136"/>
+      <c r="B123" s="146"/>
+      <c r="C123" s="133"/>
       <c r="D123" s="47" t="s">
         <v>177</v>
       </c>
@@ -10485,8 +10532,8 @@
     </row>
     <row r="124" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A124" s="138"/>
-      <c r="B124" s="145"/>
-      <c r="C124" s="136"/>
+      <c r="B124" s="146"/>
+      <c r="C124" s="133"/>
       <c r="D124" s="58" t="s">
         <v>207</v>
       </c>
@@ -10494,8 +10541,8 @@
     </row>
     <row r="125" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A125" s="138"/>
-      <c r="B125" s="145"/>
-      <c r="C125" s="136"/>
+      <c r="B125" s="146"/>
+      <c r="C125" s="133"/>
       <c r="D125" s="47" t="s">
         <v>178</v>
       </c>
@@ -10503,8 +10550,8 @@
     </row>
     <row r="126" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="138"/>
-      <c r="B126" s="145"/>
-      <c r="C126" s="136"/>
+      <c r="B126" s="146"/>
+      <c r="C126" s="133"/>
       <c r="D126" s="47" t="s">
         <v>179</v>
       </c>
@@ -10514,10 +10561,10 @@
       <c r="A127" s="137">
         <v>9</v>
       </c>
-      <c r="B127" s="146" t="s">
+      <c r="B127" s="140" t="s">
         <v>18</v>
       </c>
-      <c r="C127" s="142" t="s">
+      <c r="C127" s="143" t="s">
         <v>104</v>
       </c>
       <c r="D127" s="49" t="s">
@@ -10529,8 +10576,8 @@
     </row>
     <row r="128" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A128" s="138"/>
-      <c r="B128" s="147"/>
-      <c r="C128" s="136"/>
+      <c r="B128" s="141"/>
+      <c r="C128" s="133"/>
       <c r="D128" s="47" t="s">
         <v>181</v>
       </c>
@@ -10540,8 +10587,8 @@
     </row>
     <row r="129" spans="1:5" ht="39" x14ac:dyDescent="0.35">
       <c r="A129" s="138"/>
-      <c r="B129" s="147"/>
-      <c r="C129" s="136"/>
+      <c r="B129" s="141"/>
+      <c r="C129" s="133"/>
       <c r="D129" s="47" t="s">
         <v>182</v>
       </c>
@@ -10551,8 +10598,8 @@
     </row>
     <row r="130" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A130" s="138"/>
-      <c r="B130" s="147"/>
-      <c r="C130" s="136"/>
+      <c r="B130" s="141"/>
+      <c r="C130" s="133"/>
       <c r="D130" s="47" t="s">
         <v>183</v>
       </c>
@@ -10562,8 +10609,8 @@
     </row>
     <row r="131" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A131" s="138"/>
-      <c r="B131" s="147"/>
-      <c r="C131" s="136"/>
+      <c r="B131" s="141"/>
+      <c r="C131" s="133"/>
       <c r="D131" s="47" t="s">
         <v>184</v>
       </c>
@@ -10571,8 +10618,8 @@
     </row>
     <row r="132" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A132" s="138"/>
-      <c r="B132" s="147"/>
-      <c r="C132" s="136"/>
+      <c r="B132" s="141"/>
+      <c r="C132" s="133"/>
       <c r="D132" s="47" t="s">
         <v>185</v>
       </c>
@@ -10580,8 +10627,8 @@
     </row>
     <row r="133" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A133" s="138"/>
-      <c r="B133" s="147"/>
-      <c r="C133" s="136"/>
+      <c r="B133" s="141"/>
+      <c r="C133" s="133"/>
       <c r="D133" s="47" t="s">
         <v>186</v>
       </c>
@@ -10589,8 +10636,8 @@
     </row>
     <row r="134" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A134" s="138"/>
-      <c r="B134" s="147"/>
-      <c r="C134" s="136"/>
+      <c r="B134" s="141"/>
+      <c r="C134" s="133"/>
       <c r="D134" s="47" t="s">
         <v>187</v>
       </c>
@@ -10598,8 +10645,8 @@
     </row>
     <row r="135" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A135" s="138"/>
-      <c r="B135" s="147"/>
-      <c r="C135" s="136"/>
+      <c r="B135" s="141"/>
+      <c r="C135" s="133"/>
       <c r="D135" s="47" t="s">
         <v>188</v>
       </c>
@@ -10607,8 +10654,8 @@
     </row>
     <row r="136" spans="1:5" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="138"/>
-      <c r="B136" s="147"/>
-      <c r="C136" s="136"/>
+      <c r="B136" s="141"/>
+      <c r="C136" s="133"/>
       <c r="D136" s="47" t="s">
         <v>189</v>
       </c>
@@ -10618,10 +10665,10 @@
       <c r="A137" s="137">
         <v>10</v>
       </c>
-      <c r="B137" s="139" t="s">
+      <c r="B137" s="159" t="s">
         <v>29</v>
       </c>
-      <c r="C137" s="142" t="s">
+      <c r="C137" s="143" t="s">
         <v>109</v>
       </c>
       <c r="D137" s="49" t="s">
@@ -10633,8 +10680,8 @@
     </row>
     <row r="138" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A138" s="138"/>
-      <c r="B138" s="140"/>
-      <c r="C138" s="136"/>
+      <c r="B138" s="131"/>
+      <c r="C138" s="133"/>
       <c r="D138" s="47" t="s">
         <v>191</v>
       </c>
@@ -10644,8 +10691,8 @@
     </row>
     <row r="139" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A139" s="138"/>
-      <c r="B139" s="140"/>
-      <c r="C139" s="136"/>
+      <c r="B139" s="131"/>
+      <c r="C139" s="133"/>
       <c r="D139" s="47" t="s">
         <v>192</v>
       </c>
@@ -10655,8 +10702,8 @@
     </row>
     <row r="140" spans="1:5" ht="39" x14ac:dyDescent="0.35">
       <c r="A140" s="138"/>
-      <c r="B140" s="140"/>
-      <c r="C140" s="136"/>
+      <c r="B140" s="131"/>
+      <c r="C140" s="133"/>
       <c r="D140" s="47" t="s">
         <v>193</v>
       </c>
@@ -10664,8 +10711,8 @@
     </row>
     <row r="141" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A141" s="138"/>
-      <c r="B141" s="140"/>
-      <c r="C141" s="136"/>
+      <c r="B141" s="131"/>
+      <c r="C141" s="133"/>
       <c r="D141" s="47" t="s">
         <v>194</v>
       </c>
@@ -10673,8 +10720,8 @@
     </row>
     <row r="142" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A142" s="138"/>
-      <c r="B142" s="140"/>
-      <c r="C142" s="136"/>
+      <c r="B142" s="131"/>
+      <c r="C142" s="133"/>
       <c r="D142" s="47" t="s">
         <v>195</v>
       </c>
@@ -10682,8 +10729,8 @@
     </row>
     <row r="143" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A143" s="138"/>
-      <c r="B143" s="141"/>
-      <c r="C143" s="143"/>
+      <c r="B143" s="132"/>
+      <c r="C143" s="134"/>
       <c r="D143" s="48" t="s">
         <v>196</v>
       </c>
@@ -10691,10 +10738,10 @@
     </row>
     <row r="144" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A144" s="138"/>
-      <c r="B144" s="144" t="s">
+      <c r="B144" s="145" t="s">
         <v>43</v>
       </c>
-      <c r="C144" s="135" t="s">
+      <c r="C144" s="148" t="s">
         <v>109</v>
       </c>
       <c r="D144" s="46" t="s">
@@ -10704,8 +10751,8 @@
     </row>
     <row r="145" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A145" s="138"/>
-      <c r="B145" s="145"/>
-      <c r="C145" s="136"/>
+      <c r="B145" s="146"/>
+      <c r="C145" s="133"/>
       <c r="D145" s="47" t="s">
         <v>191</v>
       </c>
@@ -10713,8 +10760,8 @@
     </row>
     <row r="146" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A146" s="138"/>
-      <c r="B146" s="145"/>
-      <c r="C146" s="136"/>
+      <c r="B146" s="146"/>
+      <c r="C146" s="133"/>
       <c r="D146" s="47" t="s">
         <v>192</v>
       </c>
@@ -10722,8 +10769,8 @@
     </row>
     <row r="147" spans="1:5" ht="39" x14ac:dyDescent="0.35">
       <c r="A147" s="138"/>
-      <c r="B147" s="145"/>
-      <c r="C147" s="136"/>
+      <c r="B147" s="146"/>
+      <c r="C147" s="133"/>
       <c r="D147" s="47" t="s">
         <v>197</v>
       </c>
@@ -10731,8 +10778,8 @@
     </row>
     <row r="148" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A148" s="138"/>
-      <c r="B148" s="145"/>
-      <c r="C148" s="136"/>
+      <c r="B148" s="146"/>
+      <c r="C148" s="133"/>
       <c r="D148" s="47" t="s">
         <v>194</v>
       </c>
@@ -10740,8 +10787,8 @@
     </row>
     <row r="149" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A149" s="138"/>
-      <c r="B149" s="145"/>
-      <c r="C149" s="136"/>
+      <c r="B149" s="146"/>
+      <c r="C149" s="133"/>
       <c r="D149" s="47" t="s">
         <v>195</v>
       </c>
@@ -10749,8 +10796,8 @@
     </row>
     <row r="150" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A150" s="138"/>
-      <c r="B150" s="145"/>
-      <c r="C150" s="136"/>
+      <c r="B150" s="146"/>
+      <c r="C150" s="133"/>
       <c r="D150" s="47" t="s">
         <v>196</v>
       </c>
@@ -10758,8 +10805,8 @@
     </row>
     <row r="151" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="138"/>
-      <c r="B151" s="145"/>
-      <c r="C151" s="136"/>
+      <c r="B151" s="146"/>
+      <c r="C151" s="133"/>
       <c r="D151" s="47" t="s">
         <v>198</v>
       </c>
@@ -10769,10 +10816,10 @@
       <c r="A152" s="137">
         <v>11</v>
       </c>
-      <c r="B152" s="139" t="s">
+      <c r="B152" s="159" t="s">
         <v>29</v>
       </c>
-      <c r="C152" s="142" t="s">
+      <c r="C152" s="143" t="s">
         <v>211</v>
       </c>
       <c r="D152" s="49" t="s">
@@ -10784,8 +10831,8 @@
     </row>
     <row r="153" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A153" s="138"/>
-      <c r="B153" s="140"/>
-      <c r="C153" s="136"/>
+      <c r="B153" s="131"/>
+      <c r="C153" s="133"/>
       <c r="D153" s="47" t="s">
         <v>200</v>
       </c>
@@ -10795,8 +10842,8 @@
     </row>
     <row r="154" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A154" s="138"/>
-      <c r="B154" s="140"/>
-      <c r="C154" s="136"/>
+      <c r="B154" s="131"/>
+      <c r="C154" s="133"/>
       <c r="D154" s="47" t="s">
         <v>201</v>
       </c>
@@ -10806,8 +10853,8 @@
     </row>
     <row r="155" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A155" s="138"/>
-      <c r="B155" s="140"/>
-      <c r="C155" s="136"/>
+      <c r="B155" s="131"/>
+      <c r="C155" s="133"/>
       <c r="D155" s="47" t="s">
         <v>202</v>
       </c>
@@ -10815,8 +10862,8 @@
     </row>
     <row r="156" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A156" s="138"/>
-      <c r="B156" s="140"/>
-      <c r="C156" s="136"/>
+      <c r="B156" s="131"/>
+      <c r="C156" s="133"/>
       <c r="D156" s="47" t="s">
         <v>209</v>
       </c>
@@ -10824,8 +10871,8 @@
     </row>
     <row r="157" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A157" s="138"/>
-      <c r="B157" s="141"/>
-      <c r="C157" s="143"/>
+      <c r="B157" s="132"/>
+      <c r="C157" s="134"/>
       <c r="D157" s="55" t="s">
         <v>210</v>
       </c>
@@ -10833,10 +10880,10 @@
     </row>
     <row r="158" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A158" s="138"/>
-      <c r="B158" s="144" t="s">
+      <c r="B158" s="145" t="s">
         <v>43</v>
       </c>
-      <c r="C158" s="135" t="s">
+      <c r="C158" s="148" t="s">
         <v>211</v>
       </c>
       <c r="D158" s="46" t="s">
@@ -10846,8 +10893,8 @@
     </row>
     <row r="159" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A159" s="138"/>
-      <c r="B159" s="145"/>
-      <c r="C159" s="136"/>
+      <c r="B159" s="146"/>
+      <c r="C159" s="133"/>
       <c r="D159" s="47" t="s">
         <v>200</v>
       </c>
@@ -10855,8 +10902,8 @@
     </row>
     <row r="160" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A160" s="138"/>
-      <c r="B160" s="145"/>
-      <c r="C160" s="136"/>
+      <c r="B160" s="146"/>
+      <c r="C160" s="133"/>
       <c r="D160" s="47" t="s">
         <v>201</v>
       </c>
@@ -10864,8 +10911,8 @@
     </row>
     <row r="161" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A161" s="138"/>
-      <c r="B161" s="145"/>
-      <c r="C161" s="136"/>
+      <c r="B161" s="146"/>
+      <c r="C161" s="133"/>
       <c r="D161" s="47" t="s">
         <v>202</v>
       </c>
@@ -10873,8 +10920,8 @@
     </row>
     <row r="162" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A162" s="138"/>
-      <c r="B162" s="145"/>
-      <c r="C162" s="136"/>
+      <c r="B162" s="146"/>
+      <c r="C162" s="133"/>
       <c r="D162" s="47" t="s">
         <v>209</v>
       </c>
@@ -10882,8 +10929,8 @@
     </row>
     <row r="163" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A163" s="138"/>
-      <c r="B163" s="145"/>
-      <c r="C163" s="136"/>
+      <c r="B163" s="146"/>
+      <c r="C163" s="133"/>
       <c r="D163" s="47" t="s">
         <v>212</v>
       </c>
@@ -10891,17 +10938,17 @@
     </row>
     <row r="164" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A164" s="138"/>
-      <c r="B164" s="145"/>
-      <c r="C164" s="136"/>
+      <c r="B164" s="146"/>
+      <c r="C164" s="133"/>
       <c r="D164" s="47" t="s">
         <v>203</v>
       </c>
       <c r="E164" s="35"/>
     </row>
     <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A165" s="149"/>
-      <c r="B165" s="150"/>
-      <c r="C165" s="148"/>
+      <c r="A165" s="139"/>
+      <c r="B165" s="147"/>
+      <c r="C165" s="144"/>
       <c r="D165" s="57" t="s">
         <v>210</v>
       </c>
@@ -10909,42 +10956,6 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="B27:B34"/>
-    <mergeCell ref="C27:C34"/>
-    <mergeCell ref="A27:A41"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="B4:B10"/>
-    <mergeCell ref="C4:C10"/>
-    <mergeCell ref="B20:B26"/>
-    <mergeCell ref="C20:C26"/>
-    <mergeCell ref="A11:A26"/>
-    <mergeCell ref="B11:B19"/>
-    <mergeCell ref="C11:C19"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="B35:B41"/>
-    <mergeCell ref="C35:C41"/>
-    <mergeCell ref="A42:A54"/>
-    <mergeCell ref="B42:B49"/>
-    <mergeCell ref="C42:C49"/>
-    <mergeCell ref="C158:C165"/>
-    <mergeCell ref="A152:A165"/>
-    <mergeCell ref="B152:B157"/>
-    <mergeCell ref="C152:C157"/>
-    <mergeCell ref="B158:B165"/>
-    <mergeCell ref="B66:B72"/>
-    <mergeCell ref="C66:C72"/>
-    <mergeCell ref="C127:C136"/>
-    <mergeCell ref="A137:A151"/>
-    <mergeCell ref="B137:B143"/>
-    <mergeCell ref="C137:C143"/>
-    <mergeCell ref="B144:B151"/>
-    <mergeCell ref="C144:C151"/>
-    <mergeCell ref="A55:A72"/>
-    <mergeCell ref="A127:A136"/>
-    <mergeCell ref="B127:B136"/>
-    <mergeCell ref="A73:A84"/>
-    <mergeCell ref="B73:B78"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C96:C104"/>
     <mergeCell ref="A105:A126"/>
@@ -10961,6 +10972,42 @@
     <mergeCell ref="C79:C84"/>
     <mergeCell ref="B55:B65"/>
     <mergeCell ref="C55:C65"/>
+    <mergeCell ref="B66:B72"/>
+    <mergeCell ref="C66:C72"/>
+    <mergeCell ref="C127:C136"/>
+    <mergeCell ref="A137:A151"/>
+    <mergeCell ref="B137:B143"/>
+    <mergeCell ref="C137:C143"/>
+    <mergeCell ref="B144:B151"/>
+    <mergeCell ref="C144:C151"/>
+    <mergeCell ref="A55:A72"/>
+    <mergeCell ref="A127:A136"/>
+    <mergeCell ref="B127:B136"/>
+    <mergeCell ref="A73:A84"/>
+    <mergeCell ref="B73:B78"/>
+    <mergeCell ref="C158:C165"/>
+    <mergeCell ref="A152:A165"/>
+    <mergeCell ref="B152:B157"/>
+    <mergeCell ref="C152:C157"/>
+    <mergeCell ref="B158:B165"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="B35:B41"/>
+    <mergeCell ref="C35:C41"/>
+    <mergeCell ref="A42:A54"/>
+    <mergeCell ref="B42:B49"/>
+    <mergeCell ref="C42:C49"/>
+    <mergeCell ref="B27:B34"/>
+    <mergeCell ref="C27:C34"/>
+    <mergeCell ref="A27:A41"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="C4:C10"/>
+    <mergeCell ref="B20:B26"/>
+    <mergeCell ref="C20:C26"/>
+    <mergeCell ref="A11:A26"/>
+    <mergeCell ref="B11:B19"/>
+    <mergeCell ref="C11:C19"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="88" fitToHeight="0" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -10973,26 +11020,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="71a01256-664b-4da4-b4dd-5beed58790e5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7d82335c-2c29-423a-8e1d-221b76a59c5a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005230C191A4F5C54BAC11196ACFD065C0" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="92d787d678dd6f3764932783920f5cce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7d82335c-2c29-423a-8e1d-221b76a59c5a" xmlns:ns3="71a01256-664b-4da4-b4dd-5beed58790e5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b835db4a27cac5e0123106fad97b6cee" ns2:_="" ns3:_="">
     <xsd:import namespace="7d82335c-2c29-423a-8e1d-221b76a59c5a"/>
@@ -11193,7 +11220,54 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="71a01256-664b-4da4-b4dd-5beed58790e5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7d82335c-2c29-423a-8e1d-221b76a59c5a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34960DA5-42B5-45C7-BB53-3819FC61E89E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7d82335c-2c29-423a-8e1d-221b76a59c5a"/>
+    <ds:schemaRef ds:uri="71a01256-664b-4da4-b4dd-5beed58790e5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{063E810B-0662-4D19-9D83-5806B510B321}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C66A80A-6E08-438B-9D2E-15EBAC9CDD1B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -11210,31 +11284,4 @@
     <ds:schemaRef ds:uri="7d82335c-2c29-423a-8e1d-221b76a59c5a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{063E810B-0662-4D19-9D83-5806B510B321}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34960DA5-42B5-45C7-BB53-3819FC61E89E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7d82335c-2c29-423a-8e1d-221b76a59c5a"/>
-    <ds:schemaRef ds:uri="71a01256-664b-4da4-b4dd-5beed58790e5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>